--- a/hub_route.xlsx
+++ b/hub_route.xlsx
@@ -2,38 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris Han\OneDrive\Desktop\uniuni路由图\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris Han\OneDrive\Desktop\uniuni路由图\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB3E973-9079-4725-A4E6-CA3236DF6664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C4E65F-9597-4297-81CA-0BA17B09A69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="21408" windowHeight="11904" activeTab="1" xr2:uid="{92819F8E-64BA-4D7C-AAED-BA612C1D64EA}"/>
+    <workbookView xWindow="1452" yWindow="168" windowWidth="20244" windowHeight="11904" xr2:uid="{92819F8E-64BA-4D7C-AAED-BA612C1D64EA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hub_Master" sheetId="1" r:id="rId1"/>
     <sheet name="Route_Master" sheetId="2" r:id="rId2"/>
+    <sheet name="Region_Route" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Route_Master!$B$1:$J$57</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -43,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="83">
   <si>
     <t>Origin Region</t>
   </si>
@@ -259,13 +249,49 @@
   </si>
   <si>
     <t>IAH-129</t>
+  </si>
+  <si>
+    <t>Current Maximum Capacity</t>
+  </si>
+  <si>
+    <t>Sorting Mode</t>
+  </si>
+  <si>
+    <t>Manual Sorting</t>
+  </si>
+  <si>
+    <t>Libiao Sorting Machine</t>
+  </si>
+  <si>
+    <t>Libiao Sorting Machine + 4 Manual Sorting</t>
+  </si>
+  <si>
+    <t>Manual Sorting 
+(SmartSort Machine Currently Idle)</t>
+  </si>
+  <si>
+    <t>Manual Sorting + SmartSort Machine</t>
+  </si>
+  <si>
+    <t>Manual Sorting
+ (Libiao Sorting Machine / SmartSort Machine Currently Idle)</t>
+  </si>
+  <si>
+    <t>Libiao Sorting Machine + Manual Sorting</t>
+  </si>
+  <si>
+    <t>Libiao Sorting Machine + 1 Manual Sorting Team (8 Operators)
+ (Libiao Sorting Machine Idle)</t>
+  </si>
+  <si>
+    <t>Libiao Sorting Machine +1  Large Parcel Manual Sorting Team</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +318,21 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -341,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -360,6 +401,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,19 +741,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC50873B-1806-4D3C-90E9-83E28EEFE8E9}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.88671875" customWidth="1"/>
     <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="32.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -731,8 +779,14 @@
       <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -760,8 +814,14 @@
       <c r="I2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" s="9">
+        <v>250000</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -789,8 +849,14 @@
       <c r="I3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="9">
+        <v>230000</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>61</v>
       </c>
@@ -818,8 +884,14 @@
       <c r="I4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="9">
+        <v>100000</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -847,8 +919,14 @@
       <c r="I5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="9">
+        <v>150000</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -876,8 +954,14 @@
       <c r="I6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="9">
+        <v>250000</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -905,8 +989,14 @@
       <c r="I7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="9">
+        <v>350000</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -934,8 +1024,14 @@
       <c r="I8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="9">
+        <v>230000</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>59</v>
       </c>
@@ -963,8 +1059,14 @@
       <c r="I9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="9">
+        <v>180000</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -992,8 +1094,14 @@
       <c r="I10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10" s="9">
+        <v>150000</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -1021,8 +1129,14 @@
       <c r="I11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11" s="9">
+        <v>190000</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1050,8 +1164,14 @@
       <c r="I12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12" s="9">
+        <v>200000</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
@@ -1079,8 +1199,14 @@
       <c r="I13" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13" s="9">
+        <v>100000</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
@@ -1108,8 +1234,14 @@
       <c r="I14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14" s="9">
+        <v>40000</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1137,9 +1269,19 @@
       <c r="I15" t="s">
         <v>34</v>
       </c>
+      <c r="J15" s="9">
+        <v>45000</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="142" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2619,4 +2761,322 @@
   <autoFilter ref="B1:J57" xr:uid="{8185CA26-33FC-4CC0-915B-9AA070629783}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355A6946-B7C6-49D1-BA27-8EC04E2EAD98}">
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>